--- a/results/Int Task Remove ACC -0.6/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_6_permute.xlsx
@@ -440,477 +440,477 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.60029231948025</v>
+        <v>0.6106789394290093</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6111564278359978</v>
+        <v>0.6118729597497027</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6014065256083837</v>
+        <v>0.6118729597497027</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.590184650134487</v>
+        <v>0.6164892131118755</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5903438794486435</v>
+        <v>0.6164892131118755</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5903438794486435</v>
+        <v>0.6184789809323894</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5951197611959359</v>
+        <v>0.6209464366953732</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5924136609971985</v>
+        <v>0.6195536790352061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5953592037736151</v>
+        <v>0.6195536790352061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.592772226257273</v>
+        <v>0.6166087348652337</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6009693433686378</v>
+        <v>0.6153354989584248</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6009693433686378</v>
+        <v>0.580715693864683</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6175271966861148</v>
+        <v>0.5791237997940795</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6168894812875625</v>
+        <v>0.5776117199160355</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6254058551691661</v>
+        <v>0.5850927041846581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6172480465476371</v>
+        <v>0.5823069893288424</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6347598790016841</v>
+        <v>0.5807947099153171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6367506444996049</v>
+        <v>0.5804365437262053</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6361540334102209</v>
+        <v>0.5772930617522407</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6373482532663959</v>
+        <v>0.5631665482756144</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.630265940889609</v>
+        <v>0.5571980429559984</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6152620699012699</v>
+        <v>0.5498766870724952</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5989867588254544</v>
+        <v>0.5411629725997877</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5989869583609357</v>
+        <v>0.5433522759017009</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5843033418202425</v>
+        <v>0.548206575093183</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5888780918022842</v>
+        <v>0.548206575093183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5840633006361191</v>
+        <v>0.5537784038757771</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5813550055470864</v>
+        <v>0.5550518393180675</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5812356833292096</v>
+        <v>0.5602247966733445</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5815938495183214</v>
+        <v>0.5508336592412864</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5823496899218619</v>
+        <v>0.5322900288129235</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5773345651323718</v>
+        <v>0.5354732183476866</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.57613934759879</v>
+        <v>0.5244903863805062</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5663902435131015</v>
+        <v>0.5296244343169103</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5705288089328044</v>
+        <v>0.5326088865121996</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5612561955766975</v>
+        <v>0.5356715566161975</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5347552896856119</v>
+        <v>0.5170139914279557</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5123917520013409</v>
+        <v>0.530429360448875</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5123917520013409</v>
+        <v>0.5314641514554118</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5111183165590505</v>
+        <v>0.5340507299007911</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5111979312161289</v>
+        <v>0.5200028334038359</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5151752719668612</v>
+        <v>0.5193268071928551</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4828640923929093</v>
+        <v>0.5012598670295552</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4972304475181777</v>
+        <v>0.4770238883878332</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4988223415887814</v>
+        <v>0.4785361678013584</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5051101036786362</v>
+        <v>0.4816004341892075</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4834632974435514</v>
+        <v>0.4796906800967348</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4779728791373682</v>
+        <v>0.4796906800967348</v>
       </c>
     </row>
     <row r="50">
@@ -920,407 +920,407 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4672219073995738</v>
+        <v>0.4783364327844777</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4712802595557543</v>
+        <v>0.5147482660366667</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4747441955128461</v>
+        <v>0.5195634562737946</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4917410268894015</v>
+        <v>0.519007949493579</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4995009617610204</v>
+        <v>0.505953540158511</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5330115491136633</v>
+        <v>0.5035251933498814</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5325340607066749</v>
+        <v>0.515264663862528</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5380681772832845</v>
+        <v>0.5085008101140545</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.553789777398217</v>
+        <v>0.5211559489508425</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5647720107589531</v>
+        <v>0.506546759144711</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.564174801063125</v>
+        <v>0.4925810712660925</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.564174801063125</v>
+        <v>0.4604702253154656</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5593232953683824</v>
+        <v>0.5215997158614745</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5457971841552864</v>
+        <v>0.5029782665953659</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5117378742287954</v>
+        <v>0.4894886703753661</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5072012355237008</v>
+        <v>0.4946650198338268</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5037394944569044</v>
+        <v>0.4997986686992681</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5056893551811383</v>
+        <v>0.4795434229114621</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5017900328036331</v>
+        <v>0.5025857803034536</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5017900328036331</v>
+        <v>0.5015112817361184</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5030636677814049</v>
+        <v>0.5015108826651555</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5002384449002721</v>
+        <v>0.504853700585038</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4994824049612502</v>
+        <v>0.5040585516916618</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4981293548618815</v>
+        <v>0.5043369036882138</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4994029898396533</v>
+        <v>0.5047349769736055</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4990448236505415</v>
+        <v>0.5047349769736055</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5001193222178768</v>
+        <v>0.5009545777430143</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5006764252819437</v>
+        <v>0.501352251957443</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5003978737499102</v>
+        <v>0.5025063651818567</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5003978737499102</v>
+        <v>0.5028649304419311</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5015916945351222</v>
+        <v>0.5028649304419311</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5013927576601671</v>
+        <v>0.5029443455635281</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5013927576601671</v>
+        <v>0.5122554692675452</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5023477344741442</v>
+        <v>0.5134887980780742</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5011142061281337</v>
+        <v>0.5154388583377897</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5005571030640669</v>
+        <v>0.5059287977588175</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.500954976813977</v>
+        <v>0.5050931431627171</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4998407706858434</v>
+        <v>0.5047349769736055</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5005968106248653</v>
+        <v>0.5029046380027297</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4996019267146083</v>
+        <v>0.4986866574614298</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5003182590928319</v>
+        <v>0.5015517874388423</v>
       </c>
     </row>
   </sheetData>
